--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrSecLend.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrSecLend.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ideaworkspaces\ZGBS-CP-dev\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -42,10 +42,6 @@
     <t>已完成额度</t>
   </si>
   <si>
-    <t>交易完成度(%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -75,6 +71,10 @@
   </si>
   <si>
     <t>币种</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易完成度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -438,28 +438,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>2</v>
@@ -471,10 +471,10 @@
         <v>4</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.15"/>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrSecLend.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrSecLend.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -33,48 +33,51 @@
     <t>有效状态</t>
   </si>
   <si>
-    <t>委托开始日</t>
-  </si>
-  <si>
-    <t>委托截止日</t>
+    <t>交易完成度(%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组合代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资经理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标的债券代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>借贷方向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易场所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>币种</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令开始日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令截止日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>券面总额/万元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>已完成额度</t>
-  </si>
-  <si>
-    <t>交易完成度(%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>组合代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>投资经理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>标的债券代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>借贷方向</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易场所</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>券面总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>币种</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -438,43 +441,43 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.15"/>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrSecLend.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrSecLend.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12900" windowHeight="2775"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12900" windowHeight="2772"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>组合名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,6 +73,10 @@
   </si>
   <si>
     <t>已完成额度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标的债券名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -146,6 +145,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -165,7 +232,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCEDC7"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -412,7 +479,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -420,23 +487,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.125" customWidth="1"/>
-    <col min="3" max="3" width="26.25" customWidth="1"/>
-    <col min="4" max="4" width="27.75" customWidth="1"/>
-    <col min="5" max="5" width="31.5" customWidth="1"/>
-    <col min="6" max="6" width="31.375" customWidth="1"/>
-    <col min="7" max="9" width="15.375" customWidth="1"/>
-    <col min="10" max="10" width="16.25" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="23.75" customWidth="1"/>
+    <col min="1" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="26.21875" customWidth="1"/>
+    <col min="4" max="4" width="27.77734375" customWidth="1"/>
+    <col min="5" max="6" width="31.44140625" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" customWidth="1"/>
+    <col min="8" max="10" width="15.33203125" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="23.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -453,34 +520,37 @@
         <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrSecLend.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrSecLend.xlsx
@@ -64,10 +64,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>指令截止日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>券面总额/万元</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -77,6 +73,10 @@
   </si>
   <si>
     <t>标的债券名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令结束日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -520,7 +520,7 @@
         <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -529,7 +529,7 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
@@ -538,10 +538,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrSecLend.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrSecLend.xlsx
@@ -76,7 +76,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>指令结束日</t>
+    <t>指令终止日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -479,7 +479,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
